--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NEW_YORK_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NEW_YORK_2019.xlsx
@@ -2839,7 +2839,7 @@
         <v>24</v>
       </c>
       <c r="D138">
-        <v>0.0009144947416552355</v>
+        <v>0.0009144947416552356</v>
       </c>
     </row>
     <row r="139">
@@ -3973,7 +3973,7 @@
         <v>25</v>
       </c>
       <c r="D201">
-        <v>0.0009525986892242037</v>
+        <v>0.0009525986892242036</v>
       </c>
     </row>
     <row r="202">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C232">
@@ -5881,7 +5881,7 @@
         <v>25</v>
       </c>
       <c r="D307">
-        <v>0.0009525986892242037</v>
+        <v>0.0009525986892242036</v>
       </c>
     </row>
     <row r="308">
@@ -6205,7 +6205,7 @@
         <v>245</v>
       </c>
       <c r="D325">
-        <v>0.009335467154397195</v>
+        <v>0.009335467154397196</v>
       </c>
     </row>
     <row r="326">
@@ -10021,7 +10021,7 @@
         <v>25</v>
       </c>
       <c r="D537">
-        <v>0.0009525986892242037</v>
+        <v>0.0009525986892242036</v>
       </c>
     </row>
     <row r="538">
@@ -10345,7 +10345,7 @@
         <v>24</v>
       </c>
       <c r="D555">
-        <v>0.0009144947416552355</v>
+        <v>0.0009144947416552356</v>
       </c>
     </row>
     <row r="556">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C695">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C752">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C761">
@@ -15439,7 +15439,7 @@
         <v>24</v>
       </c>
       <c r="D838">
-        <v>0.0009144947416552355</v>
+        <v>0.0009144947416552356</v>
       </c>
     </row>
     <row r="839">
@@ -18661,7 +18661,7 @@
         <v>25</v>
       </c>
       <c r="D1017">
-        <v>0.0009525986892242037</v>
+        <v>0.0009525986892242036</v>
       </c>
     </row>
     <row r="1018">
@@ -18841,7 +18841,7 @@
         <v>24</v>
       </c>
       <c r="D1027">
-        <v>0.0009144947416552355</v>
+        <v>0.0009144947416552356</v>
       </c>
     </row>
     <row r="1028">
@@ -19075,7 +19075,7 @@
         <v>256</v>
       </c>
       <c r="D1040">
-        <v>0.009754610577655845</v>
+        <v>0.009754610577655844</v>
       </c>
     </row>
     <row r="1041">
@@ -19741,7 +19741,7 @@
         <v>24</v>
       </c>
       <c r="D1077">
-        <v>0.0009144947416552355</v>
+        <v>0.0009144947416552356</v>
       </c>
     </row>
     <row r="1078">
@@ -19993,7 +19993,7 @@
         <v>24</v>
       </c>
       <c r="D1091">
-        <v>0.0009144947416552355</v>
+        <v>0.0009144947416552356</v>
       </c>
     </row>
     <row r="1092">
@@ -22513,7 +22513,7 @@
         <v>25</v>
       </c>
       <c r="D1231">
-        <v>0.0009525986892242037</v>
+        <v>0.0009525986892242036</v>
       </c>
     </row>
     <row r="1232">
@@ -23395,7 +23395,7 @@
         <v>24</v>
       </c>
       <c r="D1280">
-        <v>0.0009144947416552355</v>
+        <v>0.0009144947416552356</v>
       </c>
     </row>
     <row r="1281">
@@ -24385,7 +24385,7 @@
         <v>25</v>
       </c>
       <c r="D1335">
-        <v>0.0009525986892242037</v>
+        <v>0.0009525986892242036</v>
       </c>
     </row>
     <row r="1336">
@@ -24997,7 +24997,7 @@
         <v>24</v>
       </c>
       <c r="D1369">
-        <v>0.0009144947416552355</v>
+        <v>0.0009144947416552356</v>
       </c>
     </row>
     <row r="1370">
